--- a/Stock_Report_20260225.xlsx
+++ b/Stock_Report_20260225.xlsx
@@ -457,12 +457,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>20日均線(月線)</t>
+          <t>20日均線</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>月線位階</t>
+          <t>位階</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>20日均線(月線)</t>
+          <t>20日均線</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>月線位階</t>
+          <t>位階</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:58</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:59</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>06:28</t>
+          <t>07:59</t>
         </is>
       </c>
     </row>

--- a/Stock_Report_20260225.xlsx
+++ b/Stock_Report_20260225.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:11</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:12</t>
         </is>
       </c>
     </row>
